--- a/data/trending_integrated_20261027_10.xlsx
+++ b/data/trending_integrated_20261027_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-0.41</v>
       </c>
       <c r="E2" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G2" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H2" t="n">
         <v>0.09</v>
@@ -610,7 +610,7 @@
         <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>39927568060</v>
+        <v>40226612590</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>삼성·SK 이어 美 M사 공급망 진입 뉴스. HBM, 데이터센터 관련 성장성 부각. 보호예수 해제 전 상승 기대.</t>
+          <t>삼성, SK 이어 美 'M사' 공급망 진입 및 글로벌 메모리 빅3, 세계 최대 파운드리까지 영토 확장 뉴스. HBM + 데이터센터 성장성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['HBM', '공급망', '성장성']</t>
+          <t>['HBM', '데이터센터', '공급망']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16750</v>
+        <v>16550</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+27.38%</t>
+          <t>'+25.86%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -676,7 +676,7 @@
         <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H3" t="n">
         <v>4.13</v>
@@ -702,7 +702,7 @@
         <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>13216875190</v>
+        <v>14154038445</v>
       </c>
       <c r="P3" t="n">
         <v>28600</v>
@@ -718,12 +718,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>휴머노이드 로봇 '아틀라스' 공급망 확정 뉴스. 텐버거 기대감 및 3D센싱 기술 부각. 재탕 뉴스 경계.</t>
+          <t>휴머노이드 로봇 '아틀라스' 공급망 확정 및 텐버거 가능성 언급. 3D 센싱 기술 보유 사실과 기관 매수 부진 지적.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21800</v>
+        <v>21250</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.44%</t>
+          <t>'+11.55%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.12</v>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F4" t="n">
         <v>38</v>
       </c>
       <c r="G4" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H4" t="n">
         <v>0.3</v>
@@ -794,7 +794,7 @@
         <v>0.18</v>
       </c>
       <c r="O4" t="n">
-        <v>43849770840</v>
+        <v>47767137140</v>
       </c>
       <c r="P4" t="n">
         <v>62100</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>로봇 관련주 빅웨이브 이후 대장 가능성 언급. 흑자 기업, 테슬라 납품 및 브릴스 연계 가능성 제시.</t>
+          <t>로봇 기업 빅웨이브 및 흑자 기업으로서의 대장주 가능성 언급. 테슬라 납품 및 앤트로픽 수혜주 관련 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇주', '흑자기업', '테슬라']</t>
+          <t>['로봇', '흑자기업', '앤트로픽']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1363000</v>
+        <v>1364000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.90%</t>
+          <t>'+6.98%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="G5" t="n">
-        <v>1808</v>
+        <v>1731</v>
       </c>
       <c r="H5" t="n">
         <v>48.66</v>
@@ -886,7 +886,7 @@
         <v>48.69</v>
       </c>
       <c r="O5" t="n">
-        <v>1211666561500</v>
+        <v>1274334120000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>목표가 470만원 제시, 200돌파 및 140~148만원 예상. 엔트로픽 공모 자금 연관성 언급. 채결강도 150% 기록.</t>
+          <t>야간 선물 급등 및 내일 대폭등 기대감. 엔트로픽 공모 자금 관련 언급. 140 돌파 및 15% 상승 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['목표가', '주주환원', '채결강도']</t>
+          <t>['야간선물', '대폭등', '주주환원']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>223750</v>
+        <v>15640</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.05%</t>
+          <t>'+6.47%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.01</v>
+        <v>0.46</v>
       </c>
       <c r="E6" t="n">
-        <v>747</v>
+        <v>87</v>
       </c>
       <c r="F6" t="n">
-        <v>453</v>
+        <v>66</v>
       </c>
       <c r="G6" t="n">
-        <v>2813</v>
+        <v>284</v>
       </c>
       <c r="H6" t="n">
-        <v>46.1</v>
+        <v>7.82</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>213000</v>
+        <v>14690</v>
       </c>
       <c r="K6" t="n">
-        <v>222000</v>
+        <v>14490</v>
       </c>
       <c r="L6" t="n">
-        <v>225000</v>
+        <v>15800</v>
       </c>
       <c r="M6" t="n">
-        <v>221500</v>
+        <v>14260</v>
       </c>
       <c r="N6" t="n">
-        <v>46.11</v>
+        <v>7.36</v>
       </c>
       <c r="O6" t="n">
-        <v>840365681500</v>
+        <v>48019293445</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>49800</v>
       </c>
       <c r="Q6" t="n">
-        <v>94500</v>
+        <v>8180</v>
       </c>
       <c r="R6" t="n">
-        <v>1061000</v>
+        <v>38000</v>
       </c>
       <c r="S6" t="n">
-        <v>239000</v>
+        <v>20000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>글로벌 선물주가 호조 및 앤트로픽 상장 관련 기대감. 일부 정치적 내용 포함.</t>
+          <t>해외 수출 95%, 신약 개발 활용 등 성장성 및 확장성 강조. 거래 금액 폭등 및 외인/기관 매수 우위. 대규모 공매도 숏퀴즈 발생 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['선물주가', '앤트로픽', '주가']</t>
+          <t>['AI', '수출', '성장성']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14790</v>
+        <v>14900</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.01%</t>
+          <t>'+4.78%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G7" t="n">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="H7" t="n">
         <v>10.02</v>
@@ -1070,7 +1070,7 @@
         <v>10.03</v>
       </c>
       <c r="O7" t="n">
-        <v>22410410310</v>
+        <v>23171735665</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>영업이익 223% 폭증 등 호실적 발표. 외국인, 기관 프로그램 매수 지속. 10연상 기대감.</t>
+          <t>영업이익 223% 폭증 등 실적 호조 발표. 외국인, 기관 프로그램 매수세 유입 확인. 공매도 및 대차 물량 관련 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['영업이익', '실적', '기관매수']</t>
+          <t>['영업이익', '실적', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>61900</v>
+        <v>223000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.51%</t>
+          <t>'+4.69%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>72</v>
+        <v>764</v>
       </c>
       <c r="F8" t="n">
-        <v>51</v>
+        <v>457</v>
       </c>
       <c r="G8" t="n">
-        <v>438</v>
+        <v>2827</v>
       </c>
       <c r="H8" t="n">
-        <v>40.44</v>
+        <v>46.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>59800</v>
+        <v>213000</v>
       </c>
       <c r="K8" t="n">
-        <v>60700</v>
+        <v>222000</v>
       </c>
       <c r="L8" t="n">
-        <v>63900</v>
+        <v>225000</v>
       </c>
       <c r="M8" t="n">
-        <v>60100</v>
+        <v>221500</v>
       </c>
       <c r="N8" t="n">
-        <v>40.39</v>
+        <v>46.11</v>
       </c>
       <c r="O8" t="n">
-        <v>122481308700</v>
+        <v>878824468500</v>
       </c>
       <c r="P8" t="n">
-        <v>67300</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>23150</v>
+        <v>94500</v>
       </c>
       <c r="R8" t="n">
-        <v>159000</v>
+        <v>1061000</v>
       </c>
       <c r="S8" t="n">
-        <v>19000</v>
+        <v>239000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>삼성그룹 저평가 인식, 중동 관련 이슈와 연계한 10만원 이상 목표 전망. 공매도 상환 압박 및 6만원 이하 매수 권유.</t>
+          <t>글로벌 선물주가 상승 및 앤트로픽 상장 관련 기대감. 하지만 정치 관련 언급이 다수 포함되어 객관적 분석은 미흡.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['삼성그룹', '저평가', '공매도']</t>
+          <t>['선물주가', '앤트로픽', 'AI']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15110</v>
+        <v>62500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.86%</t>
+          <t>'+4.52%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.46</v>
+        <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F9" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="G9" t="n">
-        <v>253</v>
+        <v>458</v>
       </c>
       <c r="H9" t="n">
-        <v>7.82</v>
+        <v>40.44</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14690</v>
+        <v>59800</v>
       </c>
       <c r="K9" t="n">
-        <v>14490</v>
+        <v>60700</v>
       </c>
       <c r="L9" t="n">
-        <v>15340</v>
+        <v>63900</v>
       </c>
       <c r="M9" t="n">
-        <v>14260</v>
+        <v>60100</v>
       </c>
       <c r="N9" t="n">
-        <v>7.36</v>
+        <v>40.39</v>
       </c>
       <c r="O9" t="n">
-        <v>40061837880</v>
+        <v>135839460150</v>
       </c>
       <c r="P9" t="n">
-        <v>49800</v>
+        <v>67300</v>
       </c>
       <c r="Q9" t="n">
-        <v>8180</v>
+        <v>23150</v>
       </c>
       <c r="R9" t="n">
-        <v>38000</v>
+        <v>159000</v>
       </c>
       <c r="S9" t="n">
-        <v>20000</v>
+        <v>19000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>해외 수출 95%, 신약 개발 활용 등 장기적 성장성 언급. 대규모 공매도 숏커버링 발생 가능성. 외국인, 기관 매수세 유입.</t>
+          <t>이재용 회장의 중동 방문 및 삼성그룹의 2,000조 투자 언급. 저평가된 삼성그룹주로서 10만원 이상 목표 제시.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['의료AI', '수출', '숏커버링']</t>
+          <t>['중동', '투자', '저평가']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,77 +1292,77 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16570</v>
+        <v>13810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.66%</t>
+          <t>'+3.21%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="H10" t="n">
-        <v>27.96</v>
+        <v>2.82</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>16300</v>
+        <v>13380</v>
       </c>
       <c r="K10" t="n">
-        <v>16410</v>
+        <v>14000</v>
       </c>
       <c r="L10" t="n">
-        <v>16730</v>
+        <v>14410</v>
       </c>
       <c r="M10" t="n">
-        <v>16410</v>
+        <v>13710</v>
       </c>
       <c r="N10" t="n">
-        <v>27.94</v>
+        <v>2.82</v>
       </c>
       <c r="O10" t="n">
-        <v>16039660665</v>
+        <v>25482417135</v>
       </c>
       <c r="P10" t="n">
-        <v>35350</v>
+        <v>31500</v>
       </c>
       <c r="Q10" t="n">
-        <v>16290</v>
+        <v>1760</v>
       </c>
       <c r="R10" t="n">
-        <v>106000</v>
+        <v>-133000</v>
       </c>
       <c r="S10" t="n">
-        <v>11000</v>
+        <v>4000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>조선주 하락세 속 부진. 주가조작 및 상폐 우려 언급. ETF 주도 매매, 한화오션 실적 발표 대기.</t>
+          <t>광통신, 전선, 반도체, 우주, 방산 등 다양한 업황 언급. 미국 전력 관련 기업 주가 상승 비교. 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,20 +1371,204 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>['광통신', '업황', '공매도']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>16620</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>'+1.96%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E11" t="n">
+        <v>42</v>
+      </c>
+      <c r="F11" t="n">
+        <v>32</v>
+      </c>
+      <c r="G11" t="n">
+        <v>108</v>
+      </c>
+      <c r="H11" t="n">
+        <v>27.96</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>16300</v>
+      </c>
+      <c r="K11" t="n">
+        <v>16410</v>
+      </c>
+      <c r="L11" t="n">
+        <v>16730</v>
+      </c>
+      <c r="M11" t="n">
+        <v>16410</v>
+      </c>
+      <c r="N11" t="n">
+        <v>27.94</v>
+      </c>
+      <c r="O11" t="n">
+        <v>17389436545</v>
+      </c>
+      <c r="P11" t="n">
+        <v>35350</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>16290</v>
+      </c>
+      <c r="R11" t="n">
+        <v>106000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>11000</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>조선주 하락세 속 부진. 주가조작 및 상폐 우려 언급. ETF 주도 매매, 한화오션 실적 발표 대기.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
           <t>['조선주', '하락세', 'ETF']</t>
         </is>
       </c>
-      <c r="X10" t="n">
+      <c r="X11" t="n">
         <v>14</v>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>010140</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>한화솔루션</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>26750</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>'+0.94%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="E12" t="n">
+        <v>42</v>
+      </c>
+      <c r="F12" t="n">
+        <v>34</v>
+      </c>
+      <c r="G12" t="n">
+        <v>100</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>26500</v>
+      </c>
+      <c r="K12" t="n">
+        <v>26600</v>
+      </c>
+      <c r="L12" t="n">
+        <v>27000</v>
+      </c>
+      <c r="M12" t="n">
+        <v>25350</v>
+      </c>
+      <c r="N12" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="O12" t="n">
+        <v>26438817675</v>
+      </c>
+      <c r="P12" t="n">
+        <v>59300</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>22000</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-217000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-17000</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>3분기 AMPC 제외 시 -7천억 실적 우려 및 3분기 어닝쇼크 가능성 제기. 타 에너지 기업과의 비교 언급.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['AMPC', '실적', '어닝쇼크']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>009830</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261027_10.xlsx
+++ b/data/trending_integrated_20261027_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:Z13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,10 +578,10 @@
         <v>-0.41</v>
       </c>
       <c r="E2" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G2" t="n">
         <v>71</v>
@@ -610,7 +610,7 @@
         <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>40226612590</v>
+        <v>40920979710</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -626,12 +626,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>삼성, SK 이어 美 'M사' 공급망 진입 및 글로벌 메모리 빅3, 세계 최대 파운드리까지 영토 확장 뉴스. HBM + 데이터센터 성장성 언급.</t>
+          <t>HBM, 데이터센터 관련주로 미국 M사 공급망 진입 뉴스. 글로벌 메모리 빅3 및 세계 최대 파운드리 진입으로 인한 폭등 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16550</v>
+        <v>16670</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+25.86%</t>
+          <t>'+26.77%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -676,7 +676,7 @@
         <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H3" t="n">
         <v>4.13</v>
@@ -702,7 +702,7 @@
         <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>14154038445</v>
+        <v>14411905820</v>
       </c>
       <c r="P3" t="n">
         <v>28600</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21250</v>
+        <v>20700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+11.55%</t>
+          <t>'+8.66%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.12</v>
       </c>
       <c r="E4" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F4" t="n">
         <v>38</v>
       </c>
       <c r="G4" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H4" t="n">
         <v>0.3</v>
@@ -794,7 +794,7 @@
         <v>0.18</v>
       </c>
       <c r="O4" t="n">
-        <v>47767137140</v>
+        <v>51595830440</v>
       </c>
       <c r="P4" t="n">
         <v>62100</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>로봇 기업 빅웨이브 및 흑자 기업으로서의 대장주 가능성 언급. 테슬라 납품 및 앤트로픽 수혜주 관련 기대감.</t>
+          <t>로봇 기업으로 흑자 기업. 테슬라 폭등과 연동 가능성 언급. 새내기 유일 흑자 어닝 로봇주로서 대장주 가능성.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇', '흑자기업', '앤트로픽']</t>
+          <t>['로봇기업', '흑자기업', '대장주']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1364000</v>
+        <v>1373000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.98%</t>
+          <t>'+7.69%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="G5" t="n">
-        <v>1731</v>
+        <v>1585</v>
       </c>
       <c r="H5" t="n">
         <v>48.66</v>
@@ -886,7 +886,7 @@
         <v>48.69</v>
       </c>
       <c r="O5" t="n">
-        <v>1274334120000</v>
+        <v>1415951472500</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>야간 선물 급등 및 내일 대폭등 기대감. 엔트로픽 공모 자금 관련 언급. 140 돌파 및 15% 상승 기대.</t>
+          <t>4조원 규모 자사주 소각 예정 등 주주환원 강화 기대감. 200선 돌파 및 15% 상승 기대, 144~148 구간 지지 예상.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['야간선물', '대폭등', '주주환원']</t>
+          <t>['자사주소각', '주주환원', '실적기대']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15640</v>
+        <v>15630</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.47%</t>
+          <t>'+6.40%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.46</v>
       </c>
       <c r="E6" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="G6" t="n">
-        <v>284</v>
+        <v>327</v>
       </c>
       <c r="H6" t="n">
         <v>7.82</v>
@@ -978,7 +978,7 @@
         <v>7.36</v>
       </c>
       <c r="O6" t="n">
-        <v>48019293445</v>
+        <v>54125559365</v>
       </c>
       <c r="P6" t="n">
         <v>49800</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>해외 수출 95%, 신약 개발 활용 등 성장성 및 확장성 강조. 거래 금액 폭등 및 외인/기관 매수 우위. 대규모 공매도 숏퀴즈 발생 언급.</t>
+          <t>의료 AI 대장주로서 해외 수출 확대 및 신약 개발 활용. 11월 14일 중요한 날, 공매도 숏커버링 발생 가능성 및 성장성 확장성 확고.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['AI', '수출', '성장성']</t>
+          <t>['의료AI', '해외수출', '성장성']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14900</v>
+        <v>224000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.78%</t>
+          <t>'+5.16%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>69</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>43</v>
+        <v>471</v>
       </c>
       <c r="G7" t="n">
-        <v>218</v>
+        <v>2870</v>
       </c>
       <c r="H7" t="n">
-        <v>10.02</v>
+        <v>46.1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14220</v>
+        <v>213000</v>
       </c>
       <c r="K7" t="n">
-        <v>14390</v>
+        <v>222000</v>
       </c>
       <c r="L7" t="n">
-        <v>15150</v>
+        <v>225000</v>
       </c>
       <c r="M7" t="n">
-        <v>14390</v>
+        <v>221500</v>
       </c>
       <c r="N7" t="n">
-        <v>10.03</v>
+        <v>46.11</v>
       </c>
       <c r="O7" t="n">
-        <v>23171735665</v>
+        <v>998184036000</v>
       </c>
       <c r="P7" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>3320</v>
+        <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>170000</v>
+        <v>1061000</v>
       </c>
       <c r="S7" t="n">
-        <v>2000</v>
+        <v>239000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>영업이익 223% 폭증 등 실적 호조 발표. 외국인, 기관 프로그램 매수세 유입 확인. 공매도 및 대차 물량 관련 언급.</t>
+          <t>글로벌 선물주가 상승 및 앤트로픽 상장 관련 기대감. 하지만 정치 관련 언급이 다수 포함되어 객관적 분석은 미흡.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['영업이익', '실적', '공매도']</t>
+          <t>['선물주가', '앤트로픽', 'AI']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>223000</v>
+        <v>62800</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.69%</t>
+          <t>'+5.02%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>764</v>
+        <v>85</v>
       </c>
       <c r="F8" t="n">
-        <v>457</v>
+        <v>59</v>
       </c>
       <c r="G8" t="n">
-        <v>2827</v>
+        <v>501</v>
       </c>
       <c r="H8" t="n">
-        <v>46.1</v>
+        <v>40.44</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>213000</v>
+        <v>59800</v>
       </c>
       <c r="K8" t="n">
-        <v>222000</v>
+        <v>60700</v>
       </c>
       <c r="L8" t="n">
-        <v>225000</v>
+        <v>63900</v>
       </c>
       <c r="M8" t="n">
-        <v>221500</v>
+        <v>60100</v>
       </c>
       <c r="N8" t="n">
-        <v>46.11</v>
+        <v>40.39</v>
       </c>
       <c r="O8" t="n">
-        <v>878824468500</v>
+        <v>145000096800</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>67300</v>
       </c>
       <c r="Q8" t="n">
-        <v>94500</v>
+        <v>23150</v>
       </c>
       <c r="R8" t="n">
-        <v>1061000</v>
+        <v>159000</v>
       </c>
       <c r="S8" t="n">
-        <v>239000</v>
+        <v>19000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>글로벌 선물주가 상승 및 앤트로픽 상장 관련 기대감. 하지만 정치 관련 언급이 다수 포함되어 객관적 분석은 미흡.</t>
+          <t>이재용 회장 중동 방문 및 삼성그룹 저평가 종목 분석. 6만원 이하 매수 권유 및 10만원 목표 제시.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['선물주가', '앤트로픽', 'AI']</t>
+          <t>['삼성그룹', '저평가', '매수']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62500</v>
+        <v>14870</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.52%</t>
+          <t>'+4.57%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="F9" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="G9" t="n">
-        <v>458</v>
+        <v>218</v>
       </c>
       <c r="H9" t="n">
-        <v>40.44</v>
+        <v>10.02</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>59800</v>
+        <v>14220</v>
       </c>
       <c r="K9" t="n">
-        <v>60700</v>
+        <v>14390</v>
       </c>
       <c r="L9" t="n">
-        <v>63900</v>
+        <v>15150</v>
       </c>
       <c r="M9" t="n">
-        <v>60100</v>
+        <v>14390</v>
       </c>
       <c r="N9" t="n">
-        <v>40.39</v>
+        <v>10.03</v>
       </c>
       <c r="O9" t="n">
-        <v>135839460150</v>
+        <v>23949657595</v>
       </c>
       <c r="P9" t="n">
-        <v>67300</v>
+        <v>40350</v>
       </c>
       <c r="Q9" t="n">
-        <v>23150</v>
+        <v>3320</v>
       </c>
       <c r="R9" t="n">
-        <v>159000</v>
+        <v>170000</v>
       </c>
       <c r="S9" t="n">
-        <v>19000</v>
+        <v>2000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>이재용 회장의 중동 방문 및 삼성그룹의 2,000조 투자 언급. 저평가된 삼성그룹주로서 10만원 이상 목표 제시.</t>
+          <t>영업이익 223% 폭증 등 실적 호조. 외국인, 기관 프로그램 매수세 유입. 주주 배당 및 권리 행사 독려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['중동', '투자', '저평가']</t>
+          <t>['영업이익', '실적', '외국인매수']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13810</v>
+        <v>13790</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.21%</t>
+          <t>'+3.06%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G10" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="H10" t="n">
         <v>2.82</v>
@@ -1346,7 +1346,7 @@
         <v>2.82</v>
       </c>
       <c r="O10" t="n">
-        <v>25482417135</v>
+        <v>26717149195</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>광통신, 전선, 반도체, 우주, 방산 등 다양한 업황 언급. 미국 전력 관련 기업 주가 상승 비교. 공매도 관련 언급.</t>
+          <t>유리기판 특허 보유 및 통신, 전선, 반도체 등 다양한 업황 수혜 기대. 그러나 주가 상승이 찔끔하고 하락은 큰 패턴 반복 우려.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신', '업황', '공매도']</t>
+          <t>['유리기판', '업황', '주가패턴']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16620</v>
+        <v>16640</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.96%</t>
+          <t>'+2.09%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F11" t="n">
         <v>32</v>
       </c>
       <c r="G11" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H11" t="n">
         <v>27.96</v>
@@ -1438,7 +1438,7 @@
         <v>27.94</v>
       </c>
       <c r="O11" t="n">
-        <v>17389436545</v>
+        <v>18797279640</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>조선주 하락세 속 부진. 주가조작 및 상폐 우려 언급. ETF 주도 매매, 한화오션 실적 발표 대기.</t>
+          <t>조선주 하락세 속 삼성중공업 주주들의 힘든 상황 토로. 고점 대비 큰 폭 하락에 대한 우려 및 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['조선주', '하락세', 'ETF']</t>
+          <t>['조선주', '하락', '주가조작']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,90 +1483,182 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26750</v>
+        <v>2075</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.94%</t>
+          <t>'+1.97%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.11</v>
       </c>
       <c r="E12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G12" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="H12" t="n">
-        <v>12.32</v>
+        <v>4.89</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>26500</v>
+        <v>2035</v>
       </c>
       <c r="K12" t="n">
-        <v>26600</v>
+        <v>2035</v>
       </c>
       <c r="L12" t="n">
-        <v>27000</v>
+        <v>2145</v>
       </c>
       <c r="M12" t="n">
-        <v>25350</v>
+        <v>1953</v>
       </c>
       <c r="N12" t="n">
-        <v>12.39</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>26438817675</v>
+        <v>13112602507</v>
       </c>
       <c r="P12" t="n">
-        <v>59300</v>
+        <v>4980</v>
       </c>
       <c r="Q12" t="n">
-        <v>22000</v>
+        <v>749</v>
       </c>
       <c r="R12" t="n">
-        <v>-217000</v>
+        <v>36000</v>
       </c>
       <c r="S12" t="n">
-        <v>-17000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>3분기 AMPC 제외 시 -7천억 실적 우려 및 3분기 어닝쇼크 가능성 제기. 타 에너지 기업과의 비교 언급.</t>
+          <t>로봇 관련주로 2026 로보월드 행사 기대감 존재. 주가 변동성 수반, 개미 털기 후 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['AMPC', '실적', '어닝쇼크']</t>
+          <t>['로봇주', '로보월드', '개미털기']</t>
         </is>
       </c>
       <c r="X12" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>138360</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>한화솔루션</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>26900</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>'+1.51%</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="E13" t="n">
+        <v>43</v>
+      </c>
+      <c r="F13" t="n">
+        <v>35</v>
+      </c>
+      <c r="G13" t="n">
+        <v>107</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>26500</v>
+      </c>
+      <c r="K13" t="n">
+        <v>26600</v>
+      </c>
+      <c r="L13" t="n">
+        <v>27000</v>
+      </c>
+      <c r="M13" t="n">
+        <v>25350</v>
+      </c>
+      <c r="N13" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="O13" t="n">
+        <v>27568672800</v>
+      </c>
+      <c r="P13" t="n">
+        <v>59300</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>22000</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-217000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-17000</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>3분기 AMPC 제외 실적 악화 전망 및 실제 어닝쇼크 발생. 타 종목 대비 부진한 주가 흐름에 대한 불만 표출.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['실적악화', '어닝쇼크', '주가부진']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
         <v>2</v>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>009830</t>
         </is>

--- a/data/trending_integrated_20261027_10.xlsx
+++ b/data/trending_integrated_20261027_10.xlsx
@@ -578,13 +578,13 @@
         <v>-0.41</v>
       </c>
       <c r="E2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G2" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H2" t="n">
         <v>0.09</v>
@@ -610,7 +610,7 @@
         <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>40920979710</v>
+        <v>41087907060</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -626,12 +626,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>HBM, 데이터센터 관련주로 미국 M사 공급망 진입 뉴스. 글로벌 메모리 빅3 및 세계 최대 파운드리 진입으로 인한 폭등 기대.</t>
+          <t>HBM 및 데이터센터 관련 미국 M사 공급망 진출 뉴스, 글로벌 메모리 빅3 및 파운드리 공급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16670</v>
+        <v>16930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+26.77%</t>
+          <t>'+28.75%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G3" t="n">
         <v>126</v>
@@ -702,7 +702,7 @@
         <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>14411905820</v>
+        <v>15851026500</v>
       </c>
       <c r="P3" t="n">
         <v>28600</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20700</v>
+        <v>20750</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.66%</t>
+          <t>'+8.92%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.12</v>
       </c>
       <c r="E4" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F4" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G4" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="H4" t="n">
         <v>0.3</v>
@@ -794,7 +794,7 @@
         <v>0.18</v>
       </c>
       <c r="O4" t="n">
-        <v>51595830440</v>
+        <v>53157367315</v>
       </c>
       <c r="P4" t="n">
         <v>62100</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>로봇 기업으로 흑자 기업. 테슬라 폭등과 연동 가능성 언급. 새내기 유일 흑자 어닝 로봇주로서 대장주 가능성.</t>
+          <t>로봇 기업, 흑자 기업으로 대장주 기대감 있으나 단기 급등 후 하락.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇기업', '흑자기업', '대장주']</t>
+          <t>['로봇', '흑자', '단타']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1373000</v>
+        <v>1372000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.69%</t>
+          <t>'+7.61%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="G5" t="n">
-        <v>1585</v>
+        <v>1544</v>
       </c>
       <c r="H5" t="n">
         <v>48.66</v>
@@ -877,7 +877,7 @@
         <v>1346000</v>
       </c>
       <c r="L5" t="n">
-        <v>1375000</v>
+        <v>1380000</v>
       </c>
       <c r="M5" t="n">
         <v>1345000</v>
@@ -886,7 +886,7 @@
         <v>48.69</v>
       </c>
       <c r="O5" t="n">
-        <v>1415951472500</v>
+        <v>1565745602000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>4조원 규모 자사주 소각 예정 등 주주환원 강화 기대감. 200선 돌파 및 15% 상승 기대, 144~148 구간 지지 예상.</t>
+          <t>4조 자사주 소각 예정, AI 관련 기대감, 15% 상승 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['자사주소각', '주주환원', '실적기대']</t>
+          <t>['자사주 소각', 'AI', '주주환원']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15630</v>
+        <v>224000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.40%</t>
+          <t>'+5.16%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.46</v>
+        <v>-0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>76</v>
+        <v>463</v>
       </c>
       <c r="G6" t="n">
-        <v>327</v>
+        <v>2721</v>
       </c>
       <c r="H6" t="n">
-        <v>7.82</v>
+        <v>46.1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14690</v>
+        <v>213000</v>
       </c>
       <c r="K6" t="n">
-        <v>14490</v>
+        <v>222000</v>
       </c>
       <c r="L6" t="n">
-        <v>15800</v>
+        <v>225000</v>
       </c>
       <c r="M6" t="n">
-        <v>14260</v>
+        <v>221500</v>
       </c>
       <c r="N6" t="n">
-        <v>7.36</v>
+        <v>46.11</v>
       </c>
       <c r="O6" t="n">
-        <v>54125559365</v>
+        <v>1072478472000</v>
       </c>
       <c r="P6" t="n">
-        <v>49800</v>
+        <v>374500</v>
       </c>
       <c r="Q6" t="n">
-        <v>8180</v>
+        <v>94500</v>
       </c>
       <c r="R6" t="n">
-        <v>38000</v>
+        <v>1061000</v>
       </c>
       <c r="S6" t="n">
-        <v>20000</v>
+        <v>239000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>의료 AI 대장주로서 해외 수출 확대 및 신약 개발 활용. 11월 14일 중요한 날, 공매도 숏커버링 발생 가능성 및 성장성 확장성 확고.</t>
+          <t>글로벌 선물가 및 AI 관련 기대감 속 7% 상승 전망. 정치 관련 내용은 제외.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['의료AI', '해외수출', '성장성']</t>
+          <t>['AI', '선물가']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>224000</v>
+        <v>14940</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.16%</t>
+          <t>'+5.06%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>71</v>
       </c>
       <c r="F7" t="n">
-        <v>471</v>
+        <v>42</v>
       </c>
       <c r="G7" t="n">
-        <v>2870</v>
+        <v>226</v>
       </c>
       <c r="H7" t="n">
-        <v>46.1</v>
+        <v>10.02</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>213000</v>
+        <v>14220</v>
       </c>
       <c r="K7" t="n">
-        <v>222000</v>
+        <v>14390</v>
       </c>
       <c r="L7" t="n">
-        <v>225000</v>
+        <v>15150</v>
       </c>
       <c r="M7" t="n">
-        <v>221500</v>
+        <v>14390</v>
       </c>
       <c r="N7" t="n">
-        <v>46.11</v>
+        <v>10.03</v>
       </c>
       <c r="O7" t="n">
-        <v>998184036000</v>
+        <v>24551352845</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>94500</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>1061000</v>
+        <v>170000</v>
       </c>
       <c r="S7" t="n">
-        <v>239000</v>
+        <v>2000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>글로벌 선물주가 상승 및 앤트로픽 상장 관련 기대감. 하지만 정치 관련 언급이 다수 포함되어 객관적 분석은 미흡.</t>
+          <t>223% 영업이익 폭증 등 견조한 실적 기반, 외국인/기관 매수세 유입.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['선물주가', '앤트로픽', 'AI']</t>
+          <t>['영업이익', '실적', '외국인']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1130,13 +1130,13 @@
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F8" t="n">
         <v>59</v>
       </c>
       <c r="G8" t="n">
-        <v>501</v>
+        <v>549</v>
       </c>
       <c r="H8" t="n">
         <v>40.44</v>
@@ -1162,7 +1162,7 @@
         <v>40.39</v>
       </c>
       <c r="O8" t="n">
-        <v>145000096800</v>
+        <v>149239746250</v>
       </c>
       <c r="P8" t="n">
         <v>67300</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>이재용 회장 중동 방문 및 삼성그룹 저평가 종목 분석. 6만원 이하 매수 권유 및 10만원 목표 제시.</t>
+          <t>중동 이슈와 삼성그룹 연계 투자 기대감, 저평가 인식 속 7만원 목표.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['삼성그룹', '저평가', '매수']</t>
+          <t>['중동', '저평가', 'AI']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,70 +1207,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14870</v>
+        <v>15180</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.57%</t>
+          <t>'+3.34%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.01</v>
+        <v>0.46</v>
       </c>
       <c r="E9" t="n">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="G9" t="n">
-        <v>218</v>
+        <v>347</v>
       </c>
       <c r="H9" t="n">
-        <v>10.02</v>
+        <v>7.82</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14220</v>
+        <v>14690</v>
       </c>
       <c r="K9" t="n">
-        <v>14390</v>
+        <v>14490</v>
       </c>
       <c r="L9" t="n">
-        <v>15150</v>
+        <v>15800</v>
       </c>
       <c r="M9" t="n">
-        <v>14390</v>
+        <v>14260</v>
       </c>
       <c r="N9" t="n">
-        <v>10.03</v>
+        <v>7.36</v>
       </c>
       <c r="O9" t="n">
-        <v>23949657595</v>
+        <v>57622423720</v>
       </c>
       <c r="P9" t="n">
-        <v>40350</v>
+        <v>49800</v>
       </c>
       <c r="Q9" t="n">
-        <v>3320</v>
+        <v>8180</v>
       </c>
       <c r="R9" t="n">
-        <v>170000</v>
+        <v>38000</v>
       </c>
       <c r="S9" t="n">
-        <v>2000</v>
+        <v>20000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>영업이익 223% 폭증 등 실적 호조. 외국인, 기관 프로그램 매수세 유입. 주주 배당 및 권리 행사 독려.</t>
+          <t>해외 수출, 신약 개발 활용 등 성장성 확고, 공매도 숏커버링 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['영업이익', '실적', '외국인매수']</t>
+          <t>['의료 AI', '신약 개발', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13790</v>
+        <v>13820</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.06%</t>
+          <t>'+3.29%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F10" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G10" t="n">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="H10" t="n">
         <v>2.82</v>
@@ -1346,7 +1346,7 @@
         <v>2.82</v>
       </c>
       <c r="O10" t="n">
-        <v>26717149195</v>
+        <v>28514806545</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>유리기판 특허 보유 및 통신, 전선, 반도체 등 다양한 업황 수혜 기대. 그러나 주가 상승이 찔끔하고 하락은 큰 패턴 반복 우려.</t>
+          <t>루멘텀 등 관련주 상승 속 유리기판 특허 기대감 존재. 다만, 일부 투자자는 매도 및 공매도 우려 제기하며 변동성 경계.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['유리기판', '업황', '주가패턴']</t>
+          <t>['유리기판', '특허', '공매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16640</v>
+        <v>16670</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.09%</t>
+          <t>'+2.27%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F11" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G11" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="H11" t="n">
         <v>27.96</v>
@@ -1438,7 +1438,7 @@
         <v>27.94</v>
       </c>
       <c r="O11" t="n">
-        <v>18797279640</v>
+        <v>20293128225</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>조선주 하락세 속 삼성중공업 주주들의 힘든 상황 토로. 고점 대비 큰 폭 하락에 대한 우려 및 주가 조작 의혹 제기.</t>
+          <t>주가 조작 및 고점 대비 큰 하락률에 대한 우려, 수급 쏠림 현상.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['조선주', '하락', '주가조작']</t>
+          <t>['주가 조작', '수급']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,70 +1483,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2075</v>
+        <v>27100</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.97%</t>
+          <t>'+2.26%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.11</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F12" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="G12" t="n">
-        <v>69</v>
+        <v>115</v>
       </c>
       <c r="H12" t="n">
-        <v>4.89</v>
+        <v>12.32</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>2035</v>
+        <v>26500</v>
       </c>
       <c r="K12" t="n">
-        <v>2035</v>
+        <v>26600</v>
       </c>
       <c r="L12" t="n">
-        <v>2145</v>
+        <v>27100</v>
       </c>
       <c r="M12" t="n">
-        <v>1953</v>
+        <v>25350</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>12.39</v>
       </c>
       <c r="O12" t="n">
-        <v>13112602507</v>
+        <v>29725554200</v>
       </c>
       <c r="P12" t="n">
-        <v>4980</v>
+        <v>59300</v>
       </c>
       <c r="Q12" t="n">
-        <v>749</v>
+        <v>22000</v>
       </c>
       <c r="R12" t="n">
-        <v>36000</v>
+        <v>-217000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-17000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>로봇 관련주로 2026 로보월드 행사 기대감 존재. 주가 변동성 수반, 개미 털기 후 상승 가능성 언급.</t>
+          <t>3분기 실적 부진 예상, 경쟁사 대비 약세, 개인 투자자 간의 갈등.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['로봇주', '로보월드', '개미털기']</t>
+          <t>['실적', 'AMPC']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26900</v>
+        <v>2065</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.51%</t>
+          <t>'+1.47%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.11</v>
       </c>
       <c r="E13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F13" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G13" t="n">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="H13" t="n">
-        <v>12.32</v>
+        <v>4.89</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>26500</v>
+        <v>2035</v>
       </c>
       <c r="K13" t="n">
-        <v>26600</v>
+        <v>2035</v>
       </c>
       <c r="L13" t="n">
-        <v>27000</v>
+        <v>2145</v>
       </c>
       <c r="M13" t="n">
-        <v>25350</v>
+        <v>1953</v>
       </c>
       <c r="N13" t="n">
-        <v>12.39</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>27568672800</v>
+        <v>13622045038</v>
       </c>
       <c r="P13" t="n">
-        <v>59300</v>
+        <v>4980</v>
       </c>
       <c r="Q13" t="n">
-        <v>22000</v>
+        <v>749</v>
       </c>
       <c r="R13" t="n">
-        <v>-217000</v>
+        <v>36000</v>
       </c>
       <c r="S13" t="n">
-        <v>-17000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>3분기 AMPC 제외 실적 악화 전망 및 실제 어닝쇼크 발생. 타 종목 대비 부진한 주가 흐름에 대한 불만 표출.</t>
+          <t>로봇 관련 기대감 속 변동성 장세, 2026 로보월드 일정.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['실적악화', '어닝쇼크', '주가부진']</t>
+          <t>['로봇', '로보월드', '변동성']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>138360</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261027_10.xlsx
+++ b/data/trending_integrated_20261027_10.xlsx
@@ -578,10 +578,10 @@
         <v>-0.41</v>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2" t="n">
         <v>70</v>
@@ -610,7 +610,7 @@
         <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>41087907060</v>
+        <v>41179372800</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>HBM 및 데이터센터 관련 미국 M사 공급망 진출 뉴스, 글로벌 메모리 빅3 및 파운드리 공급.</t>
+          <t>美 M사 공급망 진입 및 글로벌 메모리 빅3 협력. HBM, 데이터센터 연계 성장 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['HBM', '데이터센터', '공급망']</t>
+          <t>['공급망', 'HBM', '데이터센터']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16930</v>
+        <v>17090</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+28.75%</t>
+          <t>'+29.96%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H3" t="n">
         <v>4.13</v>
@@ -693,7 +693,7 @@
         <v>16280</v>
       </c>
       <c r="L3" t="n">
-        <v>17080</v>
+        <v>17090</v>
       </c>
       <c r="M3" t="n">
         <v>15720</v>
@@ -702,7 +702,7 @@
         <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>15851026500</v>
+        <v>18666774185</v>
       </c>
       <c r="P3" t="n">
         <v>28600</v>
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20750</v>
+        <v>1374000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.92%</t>
+          <t>'+7.76%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="E4" t="n">
-        <v>61</v>
+        <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>41</v>
+        <v>463</v>
       </c>
       <c r="G4" t="n">
-        <v>98</v>
+        <v>1538</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3</v>
+        <v>48.66</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>19050</v>
+        <v>1275000</v>
       </c>
       <c r="K4" t="n">
-        <v>19450</v>
+        <v>1346000</v>
       </c>
       <c r="L4" t="n">
-        <v>22450</v>
+        <v>1380000</v>
       </c>
       <c r="M4" t="n">
-        <v>18430</v>
+        <v>1345000</v>
       </c>
       <c r="N4" t="n">
-        <v>0.18</v>
+        <v>48.69</v>
       </c>
       <c r="O4" t="n">
-        <v>53157367315</v>
+        <v>1654287755500</v>
       </c>
       <c r="P4" t="n">
-        <v>62100</v>
+        <v>2987000</v>
       </c>
       <c r="Q4" t="n">
-        <v>14600</v>
+        <v>501000</v>
       </c>
       <c r="R4" t="n">
-        <v>44000</v>
+        <v>94000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>52000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>로봇 기업, 흑자 기업으로 대장주 기대감 있으나 단기 급등 후 하락.</t>
+          <t>4조 자사주 소각 및 역대급 주주환원 기대감. 외국인/기관 쌍끌이 매수 포착.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇', '흑자', '단타']</t>
+          <t>['자사주소각', '주주환원', '외국인기관']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>468670</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1372000</v>
+        <v>20300</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.61%</t>
+          <t>'+6.56%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.03</v>
+        <v>0.12</v>
       </c>
       <c r="E5" t="n">
-        <v>800</v>
+        <v>62</v>
       </c>
       <c r="F5" t="n">
-        <v>466</v>
+        <v>41</v>
       </c>
       <c r="G5" t="n">
-        <v>1544</v>
+        <v>101</v>
       </c>
       <c r="H5" t="n">
-        <v>48.66</v>
+        <v>0.3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1275000</v>
+        <v>19050</v>
       </c>
       <c r="K5" t="n">
-        <v>1346000</v>
+        <v>19450</v>
       </c>
       <c r="L5" t="n">
-        <v>1380000</v>
+        <v>22450</v>
       </c>
       <c r="M5" t="n">
-        <v>1345000</v>
+        <v>18430</v>
       </c>
       <c r="N5" t="n">
-        <v>48.69</v>
+        <v>0.18</v>
       </c>
       <c r="O5" t="n">
-        <v>1565745602000</v>
+        <v>54805379365</v>
       </c>
       <c r="P5" t="n">
-        <v>2987000</v>
+        <v>62100</v>
       </c>
       <c r="Q5" t="n">
-        <v>501000</v>
+        <v>14600</v>
       </c>
       <c r="R5" t="n">
-        <v>94000</v>
+        <v>44000</v>
       </c>
       <c r="S5" t="n">
-        <v>52000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>4조 자사주 소각 예정, AI 관련 기대감, 15% 상승 기대.</t>
+          <t>흑자 기업 로봇주로서 빅웨이브 기대. 기술적 분석 및 단타 흐름 관찰.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['자사주 소각', 'AI', '주주환원']</t>
+          <t>['로봇주', '흑자기업', '기술적분석']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>468670</t>
         </is>
       </c>
     </row>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>224000</v>
+        <v>224250</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.16%</t>
+          <t>'+5.28%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="G6" t="n">
-        <v>2721</v>
+        <v>2584</v>
       </c>
       <c r="H6" t="n">
         <v>46.1</v>
@@ -978,7 +978,7 @@
         <v>46.11</v>
       </c>
       <c r="O6" t="n">
-        <v>1072478472000</v>
+        <v>1149258684750</v>
       </c>
       <c r="P6" t="n">
         <v>374500</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>글로벌 선물가 및 AI 관련 기대감 속 7% 상승 전망. 정치 관련 내용은 제외.</t>
+          <t>글로벌 선물 주가 상승 및 앤트로픽 상장 기대감. 국내 정치 관련 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['AI', '선물가']</t>
+          <t>['선물주가', '앤트로픽', '상장']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1038,13 +1038,13 @@
         <v>-0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F7" t="n">
         <v>42</v>
       </c>
       <c r="G7" t="n">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="H7" t="n">
         <v>10.02</v>
@@ -1070,7 +1070,7 @@
         <v>10.03</v>
       </c>
       <c r="O7" t="n">
-        <v>24551352845</v>
+        <v>25614846280</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>223% 영업이익 폭증 등 견조한 실적 기반, 외국인/기관 매수세 유입.</t>
+          <t>223% 영업이익 폭증 및 외국인/기관 매수세 확인. 실적 기반 긍정적 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['영업이익', '실적', '외국인']</t>
+          <t>['영업이익', '실적', '기관매수']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,79 +1115,79 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>62800</v>
+        <v>14050</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.02%</t>
+          <t>'+5.01%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="F8" t="n">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="G8" t="n">
-        <v>549</v>
+        <v>164</v>
       </c>
       <c r="H8" t="n">
-        <v>40.44</v>
+        <v>2.82</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>59800</v>
+        <v>13380</v>
       </c>
       <c r="K8" t="n">
-        <v>60700</v>
+        <v>14000</v>
       </c>
       <c r="L8" t="n">
-        <v>63900</v>
+        <v>14410</v>
       </c>
       <c r="M8" t="n">
-        <v>60100</v>
+        <v>13710</v>
       </c>
       <c r="N8" t="n">
-        <v>40.39</v>
+        <v>2.82</v>
       </c>
       <c r="O8" t="n">
-        <v>149239746250</v>
+        <v>38898935505</v>
       </c>
       <c r="P8" t="n">
-        <v>67300</v>
+        <v>31500</v>
       </c>
       <c r="Q8" t="n">
-        <v>23150</v>
+        <v>1760</v>
       </c>
       <c r="R8" t="n">
-        <v>159000</v>
+        <v>-133000</v>
       </c>
       <c r="S8" t="n">
-        <v>19000</v>
+        <v>4000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>중동 이슈와 삼성그룹 연계 투자 기대감, 저평가 인식 속 7만원 목표.</t>
+          <t>유리 기판 특허 및 통신, 전선, 반도체 등 복합 업황. 외인/프로그램 매도세 관찰.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['중동', '저평가', 'AI']</t>
+          <t>['유리기판', '특허', '업황']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15180</v>
+        <v>62600</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.34%</t>
+          <t>'+4.68%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.46</v>
+        <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="F9" t="n">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="G9" t="n">
-        <v>347</v>
+        <v>575</v>
       </c>
       <c r="H9" t="n">
-        <v>7.82</v>
+        <v>40.44</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14690</v>
+        <v>59800</v>
       </c>
       <c r="K9" t="n">
-        <v>14490</v>
+        <v>60700</v>
       </c>
       <c r="L9" t="n">
-        <v>15800</v>
+        <v>63900</v>
       </c>
       <c r="M9" t="n">
-        <v>14260</v>
+        <v>60100</v>
       </c>
       <c r="N9" t="n">
-        <v>7.36</v>
+        <v>40.39</v>
       </c>
       <c r="O9" t="n">
-        <v>57622423720</v>
+        <v>155296576900</v>
       </c>
       <c r="P9" t="n">
-        <v>49800</v>
+        <v>67300</v>
       </c>
       <c r="Q9" t="n">
-        <v>8180</v>
+        <v>23150</v>
       </c>
       <c r="R9" t="n">
-        <v>38000</v>
+        <v>159000</v>
       </c>
       <c r="S9" t="n">
-        <v>20000</v>
+        <v>19000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>해외 수출, 신약 개발 활용 등 성장성 확고, 공매도 숏커버링 기대.</t>
+          <t>중동 이슈와 삼성그룹 연계 투자 기대감, 저평가 인식 속 7만원 목표.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['의료 AI', '신약 개발', '공매도']</t>
+          <t>['중동', '저평가', 'AI']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13820</v>
+        <v>15160</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.29%</t>
+          <t>'+3.20%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="E10" t="n">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="F10" t="n">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="G10" t="n">
-        <v>162</v>
+        <v>389</v>
       </c>
       <c r="H10" t="n">
-        <v>2.82</v>
+        <v>7.82</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>13380</v>
+        <v>14690</v>
       </c>
       <c r="K10" t="n">
-        <v>14000</v>
+        <v>14490</v>
       </c>
       <c r="L10" t="n">
-        <v>14410</v>
+        <v>15800</v>
       </c>
       <c r="M10" t="n">
-        <v>13710</v>
+        <v>14260</v>
       </c>
       <c r="N10" t="n">
-        <v>2.82</v>
+        <v>7.36</v>
       </c>
       <c r="O10" t="n">
-        <v>28514806545</v>
+        <v>59232256825</v>
       </c>
       <c r="P10" t="n">
-        <v>31500</v>
+        <v>49800</v>
       </c>
       <c r="Q10" t="n">
-        <v>1760</v>
+        <v>8180</v>
       </c>
       <c r="R10" t="n">
-        <v>-133000</v>
+        <v>38000</v>
       </c>
       <c r="S10" t="n">
-        <v>4000</v>
+        <v>20000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>루멘텀 등 관련주 상승 속 유리기판 특허 기대감 존재. 다만, 일부 투자자는 매도 및 공매도 우려 제기하며 변동성 경계.</t>
+          <t>AI 신약 개발 활용 및 해외 수출 확대. 루닛스코프, 인사이트 기반 성장성 확고.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['유리기판', '특허', '공매도']</t>
+          <t>['AI신약', '해외수출', '성장성']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16670</v>
+        <v>16740</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.27%</t>
+          <t>'+2.70%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F11" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G11" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H11" t="n">
         <v>27.96</v>
@@ -1429,7 +1429,7 @@
         <v>16410</v>
       </c>
       <c r="L11" t="n">
-        <v>16730</v>
+        <v>16750</v>
       </c>
       <c r="M11" t="n">
         <v>16410</v>
@@ -1438,7 +1438,7 @@
         <v>27.94</v>
       </c>
       <c r="O11" t="n">
-        <v>20293128225</v>
+        <v>22391751785</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1498,13 +1498,13 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G12" t="n">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="H12" t="n">
         <v>12.32</v>
@@ -1521,7 +1521,7 @@
         <v>26600</v>
       </c>
       <c r="L12" t="n">
-        <v>27100</v>
+        <v>27200</v>
       </c>
       <c r="M12" t="n">
         <v>25350</v>
@@ -1530,7 +1530,7 @@
         <v>12.39</v>
       </c>
       <c r="O12" t="n">
-        <v>29725554200</v>
+        <v>31229074825</v>
       </c>
       <c r="P12" t="n">
         <v>59300</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>3분기 실적 부진 예상, 경쟁사 대비 약세, 개인 투자자 간의 갈등.</t>
+          <t>3분기 실적 예상치 하향 및 부정적 전망. 개인 매수세만 관찰됨.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['실적', 'AMPC']</t>
+          <t>['실적', 'AMPC', '개인매수']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2065</v>
+        <v>2055</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.47%</t>
+          <t>'+0.98%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.11</v>
       </c>
       <c r="E13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G13" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H13" t="n">
         <v>4.89</v>
@@ -1622,7 +1622,7 @@
         <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>13622045038</v>
+        <v>14237224780</v>
       </c>
       <c r="P13" t="n">
         <v>4980</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>로봇 관련 기대감 속 변동성 장세, 2026 로보월드 일정.</t>
+          <t>로보월드 행사 예정 속 변동성 수반. 개미 털기 및 폭포수 하락 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['로봇', '로보월드', '변동성']</t>
+          <t>['로보월드', '변동성', '단주매매']</t>
         </is>
       </c>
       <c r="X13" t="n">

--- a/data/trending_integrated_20261027_10.xlsx
+++ b/data/trending_integrated_20261027_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z13"/>
+  <dimension ref="A1:Z14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,7 +584,7 @@
         <v>32</v>
       </c>
       <c r="G2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H2" t="n">
         <v>0.09</v>
@@ -610,7 +610,7 @@
         <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>41179372800</v>
+        <v>41263160990</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -670,13 +670,13 @@
         <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F3" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G3" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="H3" t="n">
         <v>4.13</v>
@@ -702,7 +702,7 @@
         <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>18666774185</v>
+        <v>18693656755</v>
       </c>
       <c r="P3" t="n">
         <v>28600</v>
@@ -718,12 +718,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>휴머노이드 로봇 '아틀라스' 공급망 확정 및 텐버거 가능성 언급. 3D 센싱 기술 보유 사실과 기관 매수 부진 지적.</t>
+          <t>나무가, 휴머노이드 로봇 '아틀라스' 공급망 확정. 3D 센싱 기술 보유.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1374000</v>
+        <v>1370000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.76%</t>
+          <t>'+7.45%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -765,10 +765,10 @@
         <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G4" t="n">
-        <v>1538</v>
+        <v>1535</v>
       </c>
       <c r="H4" t="n">
         <v>48.66</v>
@@ -785,7 +785,7 @@
         <v>1346000</v>
       </c>
       <c r="L4" t="n">
-        <v>1380000</v>
+        <v>1381000</v>
       </c>
       <c r="M4" t="n">
         <v>1345000</v>
@@ -794,7 +794,7 @@
         <v>48.69</v>
       </c>
       <c r="O4" t="n">
-        <v>1654287755500</v>
+        <v>1777741542000</v>
       </c>
       <c r="P4" t="n">
         <v>2987000</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>4조 자사주 소각 및 역대급 주주환원 기대감. 외국인/기관 쌍끌이 매수 포착.</t>
+          <t>SK하이닉스, 4조 자사주 소각 및 주주환원 기대감. 외국인/기관 쌍끌이 매수.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['자사주소각', '주주환원', '외국인기관']</t>
+          <t>['자사주소각', '주주환원', '외국인']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20300</v>
+        <v>20350</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.56%</t>
+          <t>'+6.82%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.12</v>
       </c>
       <c r="E5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -886,7 +886,7 @@
         <v>0.18</v>
       </c>
       <c r="O5" t="n">
-        <v>54805379365</v>
+        <v>55805980590</v>
       </c>
       <c r="P5" t="n">
         <v>62100</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>흑자 기업 로봇주로서 빅웨이브 기대. 기술적 분석 및 단타 흐름 관찰.</t>
+          <t>브릴스, 로봇 기업으로 빅웨이브 기대감. 기술 특례 상장 기업.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['로봇주', '흑자기업', '기술적분석']</t>
+          <t>['로봇', '빅웨이브', '기술특례']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>224250</v>
+        <v>224000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.28%</t>
+          <t>'+5.16%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="G6" t="n">
-        <v>2584</v>
+        <v>2462</v>
       </c>
       <c r="H6" t="n">
         <v>46.1</v>
@@ -969,7 +969,7 @@
         <v>222000</v>
       </c>
       <c r="L6" t="n">
-        <v>225000</v>
+        <v>225500</v>
       </c>
       <c r="M6" t="n">
         <v>221500</v>
@@ -978,7 +978,7 @@
         <v>46.11</v>
       </c>
       <c r="O6" t="n">
-        <v>1149258684750</v>
+        <v>1257822076500</v>
       </c>
       <c r="P6" t="n">
         <v>374500</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>글로벌 선물 주가 상승 및 앤트로픽 상장 기대감. 국내 정치 관련 언급.</t>
+          <t>삼성전자/하이닉스 글로벌 선물주가 상승 전망. 정치적 이슈와 함께 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['선물주가', '앤트로픽', '상장']</t>
+          <t>['선물주가', '삼성전자', '하이닉스']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14940</v>
+        <v>14950</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.06%</t>
+          <t>'+5.13%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F7" t="n">
         <v>42</v>
       </c>
       <c r="G7" t="n">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="H7" t="n">
         <v>10.02</v>
@@ -1070,7 +1070,7 @@
         <v>10.03</v>
       </c>
       <c r="O7" t="n">
-        <v>25614846280</v>
+        <v>25964427710</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>223% 영업이익 폭증 및 외국인/기관 매수세 확인. 실적 기반 긍정적 전망.</t>
+          <t>대우건설, 3분기 영업이익 223% 폭증. 외국인/기관 프로그램 매수세 유입.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['영업이익', '실적', '기관매수']</t>
+          <t>['영업이익', '외국인', '기관']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1130,13 +1130,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F8" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G8" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="H8" t="n">
         <v>2.82</v>
@@ -1162,7 +1162,7 @@
         <v>2.82</v>
       </c>
       <c r="O8" t="n">
-        <v>38898935505</v>
+        <v>43991871225</v>
       </c>
       <c r="P8" t="n">
         <v>31500</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>유리 기판 특허 및 통신, 전선, 반도체 등 복합 업황. 외인/프로그램 매도세 관찰.</t>
+          <t>대한광통신, 유리기판 특허 관련 기대감. 미국 전력 및 통신/반도체 업황 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62600</v>
+        <v>62350</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.68%</t>
+          <t>'+4.26%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F9" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G9" t="n">
-        <v>575</v>
+        <v>603</v>
       </c>
       <c r="H9" t="n">
         <v>40.44</v>
@@ -1254,7 +1254,7 @@
         <v>40.39</v>
       </c>
       <c r="O9" t="n">
-        <v>155296576900</v>
+        <v>161268283100</v>
       </c>
       <c r="P9" t="n">
         <v>67300</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>중동 이슈와 삼성그룹 연계 투자 기대감, 저평가 인식 속 7만원 목표.</t>
+          <t>삼성E&amp;A, 삼성그룹 내 저평가 종목으로 언급. 대형 수주 공시 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['중동', '저평가', 'AI']</t>
+          <t>['저평가', '대형수주', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,83 +1299,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15160</v>
+        <v>16760</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.20%</t>
+          <t>'+2.82%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.46</v>
+        <v>0.02</v>
       </c>
       <c r="E10" t="n">
-        <v>111</v>
+        <v>52</v>
       </c>
       <c r="F10" t="n">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
-        <v>389</v>
+        <v>131</v>
       </c>
       <c r="H10" t="n">
-        <v>7.82</v>
+        <v>27.96</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>14690</v>
+        <v>16300</v>
       </c>
       <c r="K10" t="n">
-        <v>14490</v>
+        <v>16410</v>
       </c>
       <c r="L10" t="n">
-        <v>15800</v>
+        <v>16770</v>
       </c>
       <c r="M10" t="n">
-        <v>14260</v>
+        <v>16410</v>
       </c>
       <c r="N10" t="n">
-        <v>7.36</v>
+        <v>27.94</v>
       </c>
       <c r="O10" t="n">
-        <v>59232256825</v>
+        <v>23464949335</v>
       </c>
       <c r="P10" t="n">
-        <v>49800</v>
+        <v>35350</v>
       </c>
       <c r="Q10" t="n">
-        <v>8180</v>
+        <v>16290</v>
       </c>
       <c r="R10" t="n">
-        <v>38000</v>
+        <v>106000</v>
       </c>
       <c r="S10" t="n">
-        <v>20000</v>
+        <v>11000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>AI 신약 개발 활용 및 해외 수출 확대. 루닛스코프, 인사이트 기반 성장성 확고.</t>
+          <t>삼성중공업, 주가 조작 및 공매도 관련 불만 표출. 조선주 하락세 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['AI신약', '해외수출', '성장성']</t>
+          <t>['주가조작', '공매도', '조선주']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16740</v>
+        <v>15080</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.70%</t>
+          <t>'+2.65%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.02</v>
+        <v>0.46</v>
       </c>
       <c r="E11" t="n">
-        <v>51</v>
+        <v>109</v>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="G11" t="n">
-        <v>124</v>
+        <v>399</v>
       </c>
       <c r="H11" t="n">
-        <v>27.96</v>
+        <v>7.82</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>16300</v>
+        <v>14690</v>
       </c>
       <c r="K11" t="n">
-        <v>16410</v>
+        <v>14490</v>
       </c>
       <c r="L11" t="n">
-        <v>16750</v>
+        <v>15800</v>
       </c>
       <c r="M11" t="n">
-        <v>16410</v>
+        <v>14260</v>
       </c>
       <c r="N11" t="n">
-        <v>27.94</v>
+        <v>7.36</v>
       </c>
       <c r="O11" t="n">
-        <v>22391751785</v>
+        <v>60041431785</v>
       </c>
       <c r="P11" t="n">
-        <v>35350</v>
+        <v>49800</v>
       </c>
       <c r="Q11" t="n">
-        <v>16290</v>
+        <v>8180</v>
       </c>
       <c r="R11" t="n">
-        <v>106000</v>
+        <v>38000</v>
       </c>
       <c r="S11" t="n">
-        <v>11000</v>
+        <v>20000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>주가 조작 및 고점 대비 큰 하락률에 대한 우려, 수급 쏠림 현상.</t>
+          <t>AI 신약 개발 활용 및 해외 수출 확대. 루닛스코프, 인사이트 기반 성장성 확고.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주가 조작', '수급']</t>
+          <t>['AI신약', '해외수출', '성장성']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
@@ -1498,13 +1498,13 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F12" t="n">
         <v>38</v>
       </c>
       <c r="G12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H12" t="n">
         <v>12.32</v>
@@ -1530,7 +1530,7 @@
         <v>12.39</v>
       </c>
       <c r="O12" t="n">
-        <v>31229074825</v>
+        <v>31907033875</v>
       </c>
       <c r="P12" t="n">
         <v>59300</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2055</v>
+        <v>2070</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.98%</t>
+          <t>'+1.72%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.11</v>
       </c>
       <c r="E13" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G13" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="H13" t="n">
         <v>4.89</v>
@@ -1622,7 +1622,7 @@
         <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>14237224780</v>
+        <v>14697832085</v>
       </c>
       <c r="P13" t="n">
         <v>4980</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>로보월드 행사 예정 속 변동성 수반. 개미 털기 및 폭포수 하락 우려.</t>
+          <t>앤로보틱스, 주가 변동성에 대한 언급. 로보월드 행사 기대감.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['로보월드', '변동성', '단주매매']</t>
+          <t>['로보월드', '변동성', '개미털기']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1661,6 +1661,98 @@
       <c r="Z13" t="inlineStr">
         <is>
           <t>138360</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>35700</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>'-2.19%</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E14" t="n">
+        <v>47</v>
+      </c>
+      <c r="F14" t="n">
+        <v>32</v>
+      </c>
+      <c r="G14" t="n">
+        <v>42</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>36500</v>
+      </c>
+      <c r="K14" t="n">
+        <v>38750</v>
+      </c>
+      <c r="L14" t="n">
+        <v>42150</v>
+      </c>
+      <c r="M14" t="n">
+        <v>35000</v>
+      </c>
+      <c r="N14" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="O14" t="n">
+        <v>60250730675</v>
+      </c>
+      <c r="P14" t="n">
+        <v>126600</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>15260</v>
+      </c>
+      <c r="R14" t="n">
+        <v>36000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈, 영업이익 157% 상승에도 컨센서스 미달. 외국인/기관 순매수.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>['영업이익', '컨센서스', '외국인']</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>327260</t>
         </is>
       </c>
     </row>
